--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "金花股份的利润总额在报告期内呈上升趋势。最新值为34207000.00万元。 数据详情： 2025FY: 0.00万元； 2025FY: 34207000.00万元； 2025FY: 34207000.00万元；", "image": ["d:\\AppGallery\\AcodeProject\\tidiCup26-B\\result\\B1002_1.jpg"]}}]</t>
+          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "金花股份的利润总额在报告期内呈上升趋势。\n最新值（2025FY）为34207000.00万元，较2025FY的0.00万元上升了0.0%。\n\n详细数据如下：\n  • 2025FY: 0.00万元\n  • 2025FY: 34207000.00万元\n  • 2025FY: 34207000.00万元\n", "image": ["d:\\AppGallery\\AcodeProject\\tidiCup26-B\\result\\B1002_1.jpg"]}}]</t>
         </is>
       </c>
     </row>

--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -456,8 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELECT TOP 1 [report_period], [total_profit] FROM income_sheet WHERE [stock_abbr] = '金花股份' ORDER BY [report_year] DESC, [report_period] DESC;
-SELECT TOP 1 [report_period], [total_profit] FROM income_sheet WHERE [stock_abbr] = '金花股份' ORDER BY [report_year] DESC, [report_period] DESC</t>
+          <t>SELECT TOP 1 [report_period], [report_year], [total_profit] FROM (SELECT DISTINCT [report_period], [report_year], [total_profit] FROM income_sheet WHERE [stock_abbr] = '金花股份' ORDER BY [report_year] DESC, [report_period] DESC) AS t</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -467,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{"Q": "金花股份利润总额是多少", "A": {"content": "金花股份2025FY的利润总额为0.00万元。"}}, {"Q": "2025年第三季度的", "A": {"content": "金花股份2025FY的利润总额为0.00万元。"}}]</t>
+          <t>[{"Q": "金花股份利润总额是多少", "A": {"content": "未找到相关数据，请检查查询条件"}}, {"Q": "2025年第三季度的", "A": {"content": "请补充以下信息：公司名称, 财务指标。"}}]</t>
         </is>
       </c>
     </row>
@@ -484,17 +483,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELECT TOP 3 [report_period], [total_profit] FROM income_sheet WHERE [stock_abbr] = '金花股份' AND [report_period] LIKE '%FY' ORDER BY [report_year] DESC</t>
+          <t>SELECT TOP 3 [report_period], [report_year], [total_profit] FROM (SELECT DISTINCT [report_period], [report_year], [total_profit] FROM income_sheet WHERE [stock_abbr] = '金花股份' AND [report_period] LIKE '%FY' ORDER BY [report_year] DESC) AS t</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>折线图</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "金花股份的利润总额在报告期内呈上升趋势。\n最新值（2025FY）为34207000.00万元，较2025FY的0.00万元上升了0.0%。\n\n详细数据如下：\n  • 2025FY: 0.00万元\n  • 2025FY: 34207000.00万元\n  • 2025FY: 34207000.00万元\n", "image": ["d:\\AppGallery\\AcodeProject\\tidiCup26-B\\result\\B1002_1.jpg"]}}]</t>
+          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "未找到相关数据，请检查查询条件"}}]</t>
         </is>
       </c>
     </row>
